--- a/artfynd/A 32580-2025 artfynd.xlsx
+++ b/artfynd/A 32580-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124290010</v>
+        <v>124285873</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Märaflotjärnen, Märaflotjärnen, Jmt</t>
+          <t>Blektjärnen, Blektjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527732</v>
+        <v>528125</v>
       </c>
       <c r="R2" t="n">
-        <v>6963314</v>
+        <v>6963503</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124288605</v>
+        <v>124287969</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bräcke kommun, Bräcke kommun, Jmt</t>
+          <t>Märaflotjärnen, Märaflotjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527888</v>
+        <v>527913</v>
       </c>
       <c r="R3" t="n">
-        <v>6963297</v>
+        <v>6963290</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,50 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124287969</v>
+        <v>124287622</v>
       </c>
       <c r="B4" t="n">
-        <v>92293</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Märaflotjärnen, Märaflotjärnen, Jmt</t>
+          <t>Blektjärnen, Blektjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527913</v>
+        <v>528053</v>
       </c>
       <c r="R4" t="n">
-        <v>6963290</v>
+        <v>6963339</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124287622</v>
+        <v>124287866</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,34 +977,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Blektjärnen, Blektjärnen, Jmt</t>
+          <t>Bräcke kommun, Bräcke kommun, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528053</v>
+        <v>527912</v>
       </c>
       <c r="R5" t="n">
-        <v>6963339</v>
+        <v>6963347</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,12 +1036,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,65 +1061,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124290083</v>
+        <v>124288605</v>
       </c>
       <c r="B6" t="n">
-        <v>96985</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Märaflotjärnen, Märaflotjärnen, Jmt</t>
+          <t>Bräcke kommun, Bräcke kommun, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527711</v>
+        <v>527888</v>
       </c>
       <c r="R6" t="n">
         <v>6963297</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1167,22 +1143,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:39</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:39</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,71 +1159,65 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124287866</v>
+        <v>124286906</v>
       </c>
       <c r="B7" t="n">
-        <v>57635</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>27</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bräcke kommun, Bräcke kommun, Jmt</t>
+          <t>Blektjärnen, Blektjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527912</v>
+        <v>528172</v>
       </c>
       <c r="R7" t="n">
-        <v>6963347</v>
+        <v>6963410</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,11 +1252,6 @@
           <t>2025-04-21</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1318,6 +1273,355 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124288215</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Blektjärnen, Blektjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>528095</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6963439</v>
+      </c>
+      <c r="S8" t="n">
+        <v>7</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Minst 90 plantor och 4 vinterståndare inom ca 2 m2.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124290010</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Märaflotjärnen, Märaflotjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>527732</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6963314</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124290083</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Märaflotjärnen, Märaflotjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>527711</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6963297</v>
+      </c>
+      <c r="S10" t="n">
+        <v>8</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32580-2025 artfynd.xlsx
+++ b/artfynd/A 32580-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124285873</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124287969</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124287622</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124287866</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124288605</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1273,6 +1303,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124286906</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1404,6 +1439,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124288215</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1510,6 +1550,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124290010</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1622,8 +1667,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124290083</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>